--- a/templet/PREMIUM_SUMMARY.xlsx
+++ b/templet/PREMIUM_SUMMARY.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64cd5bb3604bb353/Desktop/共保志工險/規格書/產出範例/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Health-and-Injury-Co-Insurance-System\templet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_AD4DBB64A54DDB1B405E389605D904C94E90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEDE3555-DF82-4875-9429-410FCCE077C9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7626EB-2F9B-47EF-BCD9-CA4E792B44DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="481" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -898,10 +898,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1318,7 +1314,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="15"/>
       <c r="D7" s="14"/>
-      <c r="E7" s="35"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="14"/>
@@ -1332,7 +1328,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="18"/>
       <c r="D8" s="14"/>
-      <c r="E8" s="35"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="15"/>
       <c r="G8" s="18"/>
       <c r="H8" s="14"/>
@@ -1346,7 +1342,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="18"/>
       <c r="D9" s="14"/>
-      <c r="E9" s="35"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="15"/>
       <c r="G9" s="18"/>
       <c r="H9" s="14"/>
@@ -1360,7 +1356,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="18"/>
       <c r="D10" s="14"/>
-      <c r="E10" s="35"/>
+      <c r="E10" s="34"/>
       <c r="F10" s="15"/>
       <c r="G10" s="18"/>
       <c r="H10" s="14"/>
@@ -1374,7 +1370,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="18"/>
       <c r="D11" s="14"/>
-      <c r="E11" s="35"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="15"/>
       <c r="G11" s="18"/>
       <c r="H11" s="14"/>
@@ -1388,7 +1384,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="18"/>
       <c r="D12" s="14"/>
-      <c r="E12" s="35"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="15"/>
       <c r="G12" s="18"/>
       <c r="H12" s="14"/>
@@ -1402,7 +1398,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="18"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="35"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="15"/>
       <c r="G13" s="18"/>
       <c r="H13" s="14"/>
@@ -1416,7 +1412,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="18"/>
       <c r="D14" s="14"/>
-      <c r="E14" s="35"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="15"/>
       <c r="G14" s="18"/>
       <c r="H14" s="14"/>

--- a/templet/PREMIUM_SUMMARY.xlsx
+++ b/templet/PREMIUM_SUMMARY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Health-and-Injury-Co-Insurance-System\templet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7626EB-2F9B-47EF-BCD9-CA4E792B44DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF97DAAF-1BBA-4B84-B5EF-ED5D4690FB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="481" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,10 +171,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(9)=(6)x5%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>(10)=(4)+(8)+(9)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -276,6 +272,10 @@
   </si>
   <si>
     <t>Ｕ/Y：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(9)=(6)x6%</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1197,7 +1197,7 @@
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -1211,20 +1211,20 @@
     </row>
     <row r="3" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="2"/>
       <c r="E3" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="6"/>
       <c r="J3" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1301,15 +1301,15 @@
         <v>19</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="33" t="s">
         <v>20</v>
-      </c>
-      <c r="J6" s="33" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="15"/>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="8" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="18"/>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="9" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="18"/>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="10" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="18"/>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="11" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="18"/>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="12" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="18"/>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="13" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="18"/>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="18"/>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="18"/>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="16" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="18"/>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="17" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="18"/>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="18" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="18"/>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="19" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="18"/>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="20" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="18"/>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="21" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="18"/>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="22" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="18"/>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="22.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="22"/>
@@ -1562,20 +1562,20 @@
     <row r="25" spans="1:12" s="1" customFormat="1" ht="22.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
       <c r="B25" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" s="40"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>

--- a/templet/PREMIUM_SUMMARY.xlsx
+++ b/templet/PREMIUM_SUMMARY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Health-and-Injury-Co-Insurance-System\templet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF97DAAF-1BBA-4B84-B5EF-ED5D4690FB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D19D6B-889D-4901-917A-07D869E602CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="481" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t>同業納入共保明細</t>
   </si>
   <si>
-    <t>共保回分同業明細</t>
-  </si>
-  <si>
     <r>
       <t>應繳共保管理會費</t>
     </r>
@@ -151,10 +148,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(4) = (2) + (3)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>查成分表</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -276,6 +269,14 @@
   </si>
   <si>
     <t>(9)=(6)x6%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>共保回分同業明細</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(4) = (2) - (3)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1197,7 +1198,7 @@
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -1211,20 +1212,20 @@
     </row>
     <row r="3" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="2"/>
       <c r="E3" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="6"/>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1237,79 +1238,79 @@
       <c r="C4" s="47"/>
       <c r="D4" s="48"/>
       <c r="E4" s="46" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="47"/>
       <c r="H4" s="48"/>
       <c r="I4" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="51" t="s">
         <v>4</v>
-      </c>
-      <c r="J4" s="51" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="45"/>
       <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>12</v>
       </c>
       <c r="I5" s="50"/>
       <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="C6" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="29" t="s">
+      <c r="F6" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="G6" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="H6" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="I6" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="33" t="s">
         <v>18</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="33" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="15"/>
@@ -1323,7 +1324,7 @@
     </row>
     <row r="8" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="18"/>
@@ -1337,7 +1338,7 @@
     </row>
     <row r="9" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="18"/>
@@ -1351,7 +1352,7 @@
     </row>
     <row r="10" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="18"/>
@@ -1365,7 +1366,7 @@
     </row>
     <row r="11" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="18"/>
@@ -1379,7 +1380,7 @@
     </row>
     <row r="12" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="18"/>
@@ -1393,7 +1394,7 @@
     </row>
     <row r="13" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="18"/>
@@ -1407,7 +1408,7 @@
     </row>
     <row r="14" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="18"/>
@@ -1421,7 +1422,7 @@
     </row>
     <row r="15" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="18"/>
@@ -1435,7 +1436,7 @@
     </row>
     <row r="16" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="18"/>
@@ -1449,7 +1450,7 @@
     </row>
     <row r="17" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="18"/>
@@ -1463,7 +1464,7 @@
     </row>
     <row r="18" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="18"/>
@@ -1477,7 +1478,7 @@
     </row>
     <row r="19" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="18"/>
@@ -1491,7 +1492,7 @@
     </row>
     <row r="20" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="18"/>
@@ -1505,7 +1506,7 @@
     </row>
     <row r="21" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="18"/>
@@ -1519,7 +1520,7 @@
     </row>
     <row r="22" spans="1:12" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="18"/>
@@ -1533,7 +1534,7 @@
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="22.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="22"/>
@@ -1562,20 +1563,20 @@
     <row r="25" spans="1:12" s="1" customFormat="1" ht="22.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="23"/>
       <c r="B25" s="23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E25" s="40"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
